--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2018_valparaiso.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2018_valparaiso.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:36</t>
+    <t xml:space="preserve">2026-10-05 01:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -701,7 +701,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>713910.62</v>
+        <v>713910.63</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>784967.44</v>
@@ -726,7 +726,7 @@
         <v>728470.88</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -734,10 +734,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>724390.12</v>
+        <v>724390.13</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -778,7 +778,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>724673.62</v>
+        <v>724673.63</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>803301.44</v>
@@ -811,7 +811,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>747573.62</v>
+        <v>747573.63</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>816660.56</v>
@@ -836,7 +836,7 @@
         <v>753658.5</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -855,7 +855,7 @@
         <v>17</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>766752.62</v>
+        <v>766752.63</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>844828.88</v>
@@ -866,7 +866,7 @@
         <v>18</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>765694.62</v>
+        <v>765694.63</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>845150.88</v>
@@ -913,7 +913,7 @@
         <v>770239.81</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -1001,7 +1001,7 @@
         <v>816777.81</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>815779.88</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1097,7 +1097,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>850851.62</v>
+        <v>850851.63</v>
       </c>
       <c r="C38" s="2" t="n">
         <v>917146.44</v>
@@ -1141,7 +1141,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>850378.12</v>
+        <v>850378.13</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>927625.75</v>
@@ -1166,7 +1166,7 @@
         <v>875686.94</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1287,7 +1287,7 @@
         <v>968939.5</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>984026.06</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1342,7 +1342,7 @@
         <v>1025165.69</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1364,7 +1364,7 @@
         <v>1068983.25</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1416,10 +1416,10 @@
         <v>68</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>1105314.12</v>
+        <v>1105314.13</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1438,7 +1438,7 @@
         <v>70</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>1111829.62</v>
+        <v>1111829.63</v>
       </c>
       <c r="C69" s="2" t="n">
         <v>1186515.5</v>
@@ -1471,7 +1471,7 @@
         <v>73</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>1149359.12</v>
+        <v>1149359.13</v>
       </c>
       <c r="C72" s="2" t="n">
         <v>1219650.75</v>
@@ -1493,7 +1493,7 @@
         <v>75</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>1153830.12</v>
+        <v>1153830.13</v>
       </c>
       <c r="C74" s="2" t="n">
         <v>1224566.38</v>
@@ -1518,7 +1518,7 @@
         <v>1160316.38</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1551,7 +1551,7 @@
         <v>1171253.5</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1194312.25</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1242405.88</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
